--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:15</t>
+    <t xml:space="preserve">2026-09-29 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:03</t>
+    <t xml:space="preserve">2026-09-29 18:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -521,10 +521,10 @@
         <v>19.71</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>51.74</v>
+        <v>51.75</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
     </row>
     <row r="5">
@@ -538,7 +538,7 @@
         <v>48.48</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>31.73</v>
+        <v>31.72</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:43</t>
+    <t xml:space="preserve">2026-10-05 04:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -524,7 +524,7 @@
         <v>51.75</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32.03</v>
+        <v>32.04</v>
       </c>
     </row>
     <row r="5">
@@ -535,10 +535,10 @@
         <v>16.76</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>48.48</v>
+        <v>48.49</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>31.72</v>
+        <v>31.73</v>
       </c>
     </row>
   </sheetData>
